--- a/data/raw_data/Table_S1.xlsx
+++ b/data/raw_data/Table_S1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Legend" sheetId="1" state="visible" r:id="rId3"/>
@@ -1515,7 +1515,7 @@
     <numFmt numFmtId="167" formatCode="0.0_ "/>
     <numFmt numFmtId="168" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1543,19 +1543,25 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1633,43 +1639,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1696,9 +1702,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>514080</xdr:colOff>
+      <xdr:colOff>513720</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>151920</xdr:rowOff>
+      <xdr:rowOff>151560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1708,7 +1714,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="7581600" cy="3009600"/>
+          <a:ext cx="7581240" cy="3009240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1718,9 +1724,7 @@
         </a:solidFill>
         <a:ln w="9525">
           <a:solidFill>
-            <a:srgbClr val="ffffff">
-              <a:shade val="50000"/>
-            </a:srgbClr>
+            <a:srgbClr val="bcbcbc"/>
           </a:solidFill>
           <a:round/>
         </a:ln>
@@ -1792,16 +1796,7 @@
               </a:solidFill>
               <a:latin typeface="Arial"/>
             </a:rPr>
-            <a:t>b MS ID, the ID of the sample analyzed for TMT-based shotgun proteomics.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-            </a:rPr>
-            <a:t> The number after "F" indicates the batch ID. The ID after "_" denotes the label for </a:t>
+            <a:t>b MS ID, the ID of the sample analyzed for TMT-based shotgun proteomics. The number after "F" indicates the batch ID. The ID after "_" denotes the label for </a:t>
           </a:r>
           <a:r>
             <a:rPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
@@ -2331,7 +2326,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="2" width="9.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="11.67"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="15" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="11.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="17.26"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="18" style="3" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="3" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="3" width="10.17"/>
